--- a/dcf/ASML.xlsx
+++ b/dcf/ASML.xlsx
@@ -849,7 +849,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1105,25 +1105,25 @@
         </is>
       </c>
       <c r="B4" s="52" t="n">
-        <v>0.09436690925679783</v>
+        <v>0.09436439541770293</v>
       </c>
       <c r="C4" s="52" t="n">
-        <v>0.09936690925679784</v>
+        <v>0.09936439541770294</v>
       </c>
       <c r="D4" s="52" t="n">
-        <v>0.1043669092567978</v>
+        <v>0.1043643954177029</v>
       </c>
       <c r="E4" s="52" t="n">
-        <v>0.1093669092567978</v>
+        <v>0.1093643954177029</v>
       </c>
       <c r="F4" s="52" t="n">
-        <v>0.1143669092567978</v>
+        <v>0.1143643954177029</v>
       </c>
       <c r="G4" s="52" t="n">
-        <v>0.1193669092567978</v>
+        <v>0.1193643954177029</v>
       </c>
       <c r="H4" s="52" t="n">
-        <v>0.1243669092567978</v>
+        <v>0.1243643954177029</v>
       </c>
     </row>
     <row r="5">
@@ -1131,25 +1131,25 @@
         <v>13</v>
       </c>
       <c r="B5" s="54" t="n">
-        <v>739.8533986479813</v>
+        <v>637.0027091007713</v>
       </c>
       <c r="C5" s="54" t="n">
-        <v>712.8272987123802</v>
+        <v>614.2592101581729</v>
       </c>
       <c r="D5" s="54" t="n">
-        <v>687.0310507189329</v>
+        <v>592.5443181135668</v>
       </c>
       <c r="E5" s="54" t="n">
-        <v>662.4018730861673</v>
+        <v>571.8056651598015</v>
       </c>
       <c r="F5" s="54" t="n">
-        <v>638.880490078737</v>
+        <v>551.9938037668812</v>
       </c>
       <c r="G5" s="54" t="n">
-        <v>616.410920334294</v>
+        <v>533.0620306709876</v>
       </c>
       <c r="H5" s="54" t="n">
-        <v>594.9402790576579</v>
+        <v>514.9662222332336</v>
       </c>
     </row>
     <row r="6">
@@ -1157,25 +1157,25 @@
         <v>14</v>
       </c>
       <c r="B6" s="54" t="n">
-        <v>774.9293394683074</v>
+        <v>666.1395612681223</v>
       </c>
       <c r="C6" s="54" t="n">
-        <v>746.3402170988537</v>
+        <v>642.0976892943851</v>
       </c>
       <c r="D6" s="54" t="n">
-        <v>719.0572206511654</v>
+        <v>619.1477837052364</v>
       </c>
       <c r="E6" s="54" t="n">
-        <v>693.0135260680327</v>
+        <v>597.2341186708122</v>
       </c>
       <c r="F6" s="54" t="n">
-        <v>668.1460462173089</v>
+        <v>576.3040805925631</v>
       </c>
       <c r="G6" s="54" t="n">
-        <v>644.3952052560732</v>
+        <v>556.3079803274804</v>
       </c>
       <c r="H6" s="54" t="n">
-        <v>621.7047275880547</v>
+        <v>537.19887755124</v>
       </c>
     </row>
     <row r="7">
@@ -1183,25 +1183,25 @@
         <v>15</v>
       </c>
       <c r="B7" s="54" t="n">
-        <v>810.0052802886336</v>
+        <v>695.2764134354733</v>
       </c>
       <c r="C7" s="54" t="n">
-        <v>779.8531354853272</v>
+        <v>669.9361684305974</v>
       </c>
       <c r="D7" s="54" t="n">
-        <v>751.083390583398</v>
+        <v>645.7512492969062</v>
       </c>
       <c r="E7" s="54" t="n">
-        <v>723.6251790498984</v>
+        <v>622.6625721818231</v>
       </c>
       <c r="F7" s="54" t="n">
-        <v>697.4116023558809</v>
+        <v>600.614357418245</v>
       </c>
       <c r="G7" s="54" t="n">
-        <v>672.3794901778523</v>
+        <v>579.5539299839733</v>
       </c>
       <c r="H7" s="54" t="n">
-        <v>648.4691761184514</v>
+        <v>559.4315328692464</v>
       </c>
     </row>
     <row r="8">
@@ -1209,25 +1209,25 @@
         <v>16</v>
       </c>
       <c r="B8" s="54" t="n">
-        <v>845.0812211089595</v>
+        <v>724.4132656028244</v>
       </c>
       <c r="C8" s="54" t="n">
-        <v>813.3660538718008</v>
+        <v>697.7746475668096</v>
       </c>
       <c r="D8" s="54" t="n">
-        <v>783.1095605156305</v>
+        <v>672.354714888576</v>
       </c>
       <c r="E8" s="55" t="n">
-        <v>754.2368320317642</v>
+        <v>648.0910256928339</v>
       </c>
       <c r="F8" s="54" t="n">
-        <v>726.6771584944528</v>
+        <v>624.924634243927</v>
       </c>
       <c r="G8" s="54" t="n">
-        <v>700.3637750996314</v>
+        <v>602.7998796404663</v>
       </c>
       <c r="H8" s="54" t="n">
-        <v>675.2336246488481</v>
+        <v>581.6641881872528</v>
       </c>
     </row>
     <row r="9">
@@ -1235,25 +1235,25 @@
         <v>17</v>
       </c>
       <c r="B9" s="54" t="n">
-        <v>880.1571619292856</v>
+        <v>753.5501177701755</v>
       </c>
       <c r="C9" s="54" t="n">
-        <v>846.8789722582744</v>
+        <v>725.6131267030219</v>
       </c>
       <c r="D9" s="54" t="n">
-        <v>815.135730447863</v>
+        <v>698.9581804802458</v>
       </c>
       <c r="E9" s="54" t="n">
-        <v>784.8484850136298</v>
+        <v>673.5194792038448</v>
       </c>
       <c r="F9" s="54" t="n">
-        <v>755.9427146330247</v>
+        <v>649.2349110696091</v>
       </c>
       <c r="G9" s="54" t="n">
-        <v>728.3480600214106</v>
+        <v>626.0458292969591</v>
       </c>
       <c r="H9" s="54" t="n">
-        <v>701.998073179245</v>
+        <v>603.8968435052594</v>
       </c>
     </row>
     <row r="10">
@@ -1261,25 +1261,25 @@
         <v>18</v>
       </c>
       <c r="B10" s="54" t="n">
-        <v>915.2331027496116</v>
+        <v>782.6869699375264</v>
       </c>
       <c r="C10" s="54" t="n">
-        <v>880.3918906447479</v>
+        <v>753.4516058392342</v>
       </c>
       <c r="D10" s="54" t="n">
-        <v>847.1619003800954</v>
+        <v>725.5616460719154</v>
       </c>
       <c r="E10" s="54" t="n">
-        <v>815.4601379954955</v>
+        <v>698.9479327148557</v>
       </c>
       <c r="F10" s="54" t="n">
-        <v>785.2082707715966</v>
+        <v>673.5451878952911</v>
       </c>
       <c r="G10" s="54" t="n">
-        <v>756.3323449431897</v>
+        <v>649.2917789534523</v>
       </c>
       <c r="H10" s="54" t="n">
-        <v>728.762521709642</v>
+        <v>626.1294988232659</v>
       </c>
     </row>
     <row r="11">
@@ -1287,25 +1287,25 @@
         <v>19</v>
       </c>
       <c r="B11" s="54" t="n">
-        <v>950.3090435699377</v>
+        <v>811.8238221048774</v>
       </c>
       <c r="C11" s="54" t="n">
-        <v>913.9048090312215</v>
+        <v>781.2900849754463</v>
       </c>
       <c r="D11" s="54" t="n">
-        <v>879.188070312328</v>
+        <v>752.1651116635853</v>
       </c>
       <c r="E11" s="54" t="n">
-        <v>846.071790977361</v>
+        <v>724.3763862258666</v>
       </c>
       <c r="F11" s="54" t="n">
-        <v>814.4738269101686</v>
+        <v>697.8554647209728</v>
       </c>
       <c r="G11" s="54" t="n">
-        <v>784.3166298649689</v>
+        <v>672.537728609945</v>
       </c>
       <c r="H11" s="54" t="n">
-        <v>755.5269702400385</v>
+        <v>648.3621541412722</v>
       </c>
     </row>
     <row r="13">
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="B13" s="54" t="n">
-        <v>1769.319946289062</v>
+        <v>1754.099853515625</v>
       </c>
     </row>
     <row r="14">
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="B14" s="56" t="n">
-        <v>0.1093669092567978</v>
+        <v>0.1093643954177029</v>
       </c>
       <c r="C14" s="57" t="n">
         <v>16</v>
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="I8" s="49" t="n">
-        <v>1.115483915310173</v>
+        <v>1.118650088763698</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24410,7 +24410,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>1769.319946289062</v>
+        <v>1754.099853515625</v>
       </c>
     </row>
     <row r="49">
@@ -24420,7 +24420,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24572,13 +24572,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>754.2368320317642</v>
+        <v>648.0910256928339</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>1002.860338547764</v>
+        <v>840.1267435490181</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>564.0597701935241</v>
+        <v>497.2658128013525</v>
       </c>
     </row>
     <row r="59">
